--- a/pupils-tracker/docs/References/Lesson plan info.xlsx
+++ b/pupils-tracker/docs/References/Lesson plan info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Claude\Pupils-tracker\pupils-tracker\docs\References\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94410BA5-B6E3-4359-88C3-4D45E1976E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC6E94F-AA70-4308-8A76-8C1C7231A6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,6 @@
     <t xml:space="preserve">Engagement :       / 28 </t>
   </si>
   <si>
-    <t xml:space="preserve">Remedial      :        /2 pupils </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                             / 36 pupils are </t>
-  </si>
-  <si>
     <t xml:space="preserve">                             /36  absentee.</t>
   </si>
   <si>
@@ -122,6 +116,12 @@
   </si>
   <si>
     <t>Enrichment:  / 9 pupils Engagement:  / 26 pupils Remedial:    / 3 pupils                        / 38 pupils                        / 38 absentee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedial      :        /1 pupils </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                             / 35 pupils are </t>
   </si>
 </sst>
 </file>
@@ -495,9 +495,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -555,7 +555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -584,7 +584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -613,7 +613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -642,7 +642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -700,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -729,12 +729,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -816,7 +816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -845,7 +845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -874,7 +874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -903,7 +903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -932,7 +932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -961,7 +961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -990,7 +990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -1019,999 +1019,999 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B24" t="s">
         <v>9</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
         <v>11</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>14</v>
       </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" t="s">
-        <v>2</v>
-      </c>
-      <c r="I28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F29" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" t="s">
-        <v>2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>2</v>
-      </c>
-      <c r="I29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
         <v>16</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
         <v>17</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" t="s">
-        <v>2</v>
-      </c>
-      <c r="H30" t="s">
-        <v>2</v>
-      </c>
-      <c r="I30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" t="s">
-        <v>2</v>
-      </c>
-      <c r="H31" t="s">
-        <v>2</v>
-      </c>
-      <c r="I31" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
         <v>19</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I32" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>20</v>
       </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" t="s">
-        <v>2</v>
-      </c>
-      <c r="H33" t="s">
-        <v>2</v>
-      </c>
-      <c r="I33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="B37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>2</v>
-      </c>
-      <c r="H34" t="s">
-        <v>2</v>
-      </c>
-      <c r="I34" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>2</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" t="s">
-        <v>2</v>
-      </c>
-      <c r="H35" t="s">
-        <v>2</v>
-      </c>
-      <c r="I35" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" t="s">
-        <v>2</v>
-      </c>
-      <c r="H36" t="s">
-        <v>2</v>
-      </c>
-      <c r="I36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>2</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>2</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B43" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" t="s">
-        <v>2</v>
-      </c>
-      <c r="E43" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" t="s">
-        <v>2</v>
-      </c>
-      <c r="H43" t="s">
-        <v>2</v>
-      </c>
-      <c r="I43" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>2</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F44" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" t="s">
-        <v>2</v>
-      </c>
-      <c r="H44" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>2</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>2</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>2</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" t="s">
-        <v>2</v>
-      </c>
-      <c r="H51" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" t="s">
-        <v>2</v>
-      </c>
-      <c r="H52" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>2</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>2</v>
       </c>
@@ -2189,7 +2189,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I8 A10:I58 A9 C9:I9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I8 A10:I18 A9 C9:I9 A21:I58 A19 C19:I19 A20 C20:I20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>